--- a/artfynd/A 66734-2021 artfynd.xlsx
+++ b/artfynd/A 66734-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>73100125</v>
+        <v>73100140</v>
       </c>
       <c r="B2" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -717,10 +712,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637483.8935634956</v>
+        <v>637515</v>
       </c>
       <c r="R2" t="n">
-        <v>6553015.960306553</v>
+        <v>6553029</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,19 +745,9 @@
           <t>2018-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,16 +778,11 @@
         <v>73100107</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637477.094537805</v>
+        <v>637477</v>
       </c>
       <c r="R3" t="n">
-        <v>6553018.801197273</v>
+        <v>6553019</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,19 +845,9 @@
           <t>2018-09-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +872,106 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>73100125</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stora Harsjön, V om nordspetsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>637484</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6553016</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-09-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-09-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66734-2021 artfynd.xlsx
+++ b/artfynd/A 66734-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73100140</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73100107</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,8 +987,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73100125</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>